--- a/artfynd/A 25013-2025 artfynd.xlsx
+++ b/artfynd/A 25013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69528999</v>
+        <v>56442455</v>
       </c>
       <c r="B2" t="n">
-        <v>90655</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>788</v>
+        <v>720</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rörbergmyren 7 km NNV om Skärplinge, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650813.5744813479</v>
+        <v>650842</v>
       </c>
       <c r="R2" t="n">
-        <v>6713845.413253254</v>
+        <v>6713756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +743,14 @@
           <t>2005-09-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-09-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 m2 i fuktigt parti i äldre barrskog.</t>
+          <t>1 m lång sträng på småblockig backe i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75873403</v>
+        <v>56442878</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650816.4895330783</v>
+        <v>650828</v>
       </c>
       <c r="R3" t="n">
-        <v>6713846.520605859</v>
+        <v>6713747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,24 +850,14 @@
           <t>2005-09-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-09-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>En halv häxring, 4 m i diameter, på småblockig backe i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +869,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -920,6 +886,224 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>69528999</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93199</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>788</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rörbergmyren 7 km NNV om Skärplinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>650814</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6713845</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 m2 i fuktigt parti i äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75873403</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rörbergmyren 7 km NNV om Skärplinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>650816</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6713847</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2005-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2005-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25013-2025 artfynd.xlsx
+++ b/artfynd/A 25013-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442455</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442878</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69528999</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,8 +1124,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75873403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>